--- a/dados/processados/ranking.xlsx
+++ b/dados/processados/ranking.xlsx
@@ -37,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -50,6 +50,27 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -425,582 +446,792 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>ano</t>
+          <t>GrupoIA</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>codigo_ncm</t>
+          <t>volume_kg</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>GrupoIA</t>
+          <t>valor_usd</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>qtde_paises</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>valor_usd</t>
+          <t>mais_importacao</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>qtde_paises</t>
+          <t>maior_volume</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>preco_import_brl_medio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2025</t>
+        <v>2025</v>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>CLETHODIM 240</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38089324</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>glyphosate AE 720</t>
-        </is>
+        <v>281941560</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1430041845</v>
       </c>
       <c r="E2" t="n">
-        <v>174401670</v>
-      </c>
-      <c r="F2" t="n">
-        <v>488074961</v>
-      </c>
-      <c r="G2" t="n">
+        <v>23</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>28.06</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>GLYPHOSATE AE 500/720</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>255237086</v>
+      </c>
+      <c r="D3" t="n">
+        <v>774030019</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>16.81</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n"/>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>MANCOZEB 750</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>135179320</v>
+      </c>
+      <c r="D4" t="n">
+        <v>444303735</v>
+      </c>
+      <c r="E4" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>38249986</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>mancozeb 750</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>8739725</v>
-      </c>
-      <c r="F3" t="n">
-        <v>23469217</v>
-      </c>
-      <c r="G3" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>29309039</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>clethodim 240</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>5554664</v>
-      </c>
-      <c r="F4" t="n">
-        <v>65294144</v>
-      </c>
-      <c r="G4" t="n">
-        <v>17</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Índia</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Índia</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>18.32</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2025</t>
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>2,4-D AE 670</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29221912</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2,4-D AE 670</t>
-        </is>
+        <v>100029433</v>
+      </c>
+      <c r="D5" t="n">
+        <v>182361724</v>
       </c>
       <c r="E5" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2372</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>10.06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2024</t>
+        <v>2024</v>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>CLETHODIM 240</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38089324</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>glyphosate AE 720</t>
-        </is>
+        <v>209042933</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1078469342</v>
       </c>
       <c r="E6" t="n">
-        <v>158433037</v>
-      </c>
-      <c r="F6" t="n">
-        <v>480548642</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4</v>
+        <v>22</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>28.19</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>GLYPHOSATE AE 500/720</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>236209837</v>
+      </c>
+      <c r="D7" t="n">
+        <v>772681031</v>
+      </c>
+      <c r="E7" t="n">
         <v>5</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>38249986</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>mancozeb 750</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>9522281</v>
-      </c>
-      <c r="F7" t="n">
-        <v>21245624</v>
-      </c>
-      <c r="G7" t="n">
-        <v>5</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>18.02</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>MANCOZEB 750</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>102283684</v>
+      </c>
+      <c r="D8" t="n">
+        <v>360452972</v>
+      </c>
+      <c r="E8" t="n">
         <v>6</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>29309039</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>clethodim 240</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>4537926</v>
-      </c>
-      <c r="F8" t="n">
-        <v>43920347</v>
-      </c>
-      <c r="G8" t="n">
-        <v>16</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Índia</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Índia</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>19.35</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2024</t>
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>2,4-D AE 670</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>29221912</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2,4-D AE 670</t>
-        </is>
+        <v>63513811</v>
+      </c>
+      <c r="D9" t="n">
+        <v>107120042</v>
       </c>
       <c r="E9" t="n">
-        <v>2215</v>
-      </c>
-      <c r="F9" t="n">
-        <v>6274</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Índia</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>9.31</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>CLETHODIM 240</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>142712911</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1186796989</v>
+      </c>
+      <c r="E10" t="n">
+        <v>23</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>41.33</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>GLYPHOSATE AE 500/720</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>147361473</v>
+      </c>
+      <c r="D11" t="n">
+        <v>688066162</v>
+      </c>
+      <c r="E11" t="n">
         <v>8</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>38089324</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>glyphosate AE 720</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>96771673</v>
-      </c>
-      <c r="F10" t="n">
-        <v>362298209</v>
-      </c>
-      <c r="G10" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>38249986</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>mancozeb 750</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>5606218</v>
-      </c>
-      <c r="F11" t="n">
-        <v>17622376</v>
-      </c>
-      <c r="G11" t="n">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>23.31</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>MANCOZEB 750</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>56436004</v>
+      </c>
+      <c r="D12" t="n">
+        <v>247939304</v>
+      </c>
+      <c r="E12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Índia</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Índia</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>21.64</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>2,4-D AE 670</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>71043351</v>
+      </c>
+      <c r="D13" t="n">
+        <v>176783175</v>
+      </c>
+      <c r="E13" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>29309039</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>clethodim 240</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>4531712</v>
-      </c>
-      <c r="F12" t="n">
-        <v>67776307</v>
-      </c>
-      <c r="G12" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>38089324</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>glyphosate AE 720</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>145584539</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1091867858</v>
-      </c>
-      <c r="G13" t="n">
-        <v>6</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>12.42</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2022</t>
+        <v>2022</v>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>GLYPHOSATE AE 500/720</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38249986</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>mancozeb 750</t>
-        </is>
+        <v>253976417</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2253379580</v>
       </c>
       <c r="E14" t="n">
-        <v>9346826</v>
-      </c>
-      <c r="F14" t="n">
-        <v>33140448</v>
-      </c>
-      <c r="G14" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>45.58</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2022</t>
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>CLETHODIM 240</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>29309039</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>clethodim 240</t>
-        </is>
+        <v>181007207</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1961314029</v>
       </c>
       <c r="E15" t="n">
-        <v>6865643</v>
-      </c>
-      <c r="F15" t="n">
-        <v>156425132</v>
-      </c>
-      <c r="G15" t="n">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>55.9</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2021</t>
+      <c r="A16" s="1" t="n"/>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>MANCOZEB 750</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>38089324</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>glyphosate AE 720</t>
-        </is>
+        <v>63958287</v>
+      </c>
+      <c r="D16" t="n">
+        <v>291573575</v>
       </c>
       <c r="E16" t="n">
-        <v>58601058</v>
-      </c>
-      <c r="F16" t="n">
-        <v>292488147</v>
-      </c>
-      <c r="G16" t="n">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Índia</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Índia</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>23.54</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2021</t>
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>2,4-D AE 670</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>29309039</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>clethodim 240</t>
-        </is>
+        <v>80150235</v>
+      </c>
+      <c r="D17" t="n">
+        <v>280678246</v>
       </c>
       <c r="E17" t="n">
-        <v>7756146</v>
-      </c>
-      <c r="F17" t="n">
-        <v>121304410</v>
-      </c>
-      <c r="G17" t="n">
-        <v>16</v>
+        <v>8</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>18.14</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2021</t>
+        <v>2021</v>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>CLETHODIM 240</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>38249986</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>mancozeb 750</t>
-        </is>
+        <v>102320782</v>
+      </c>
+      <c r="D18" t="n">
+        <v>934322474</v>
       </c>
       <c r="E18" t="n">
-        <v>6827552</v>
-      </c>
-      <c r="F18" t="n">
-        <v>16275812</v>
-      </c>
-      <c r="G18" t="n">
-        <v>7</v>
+        <v>21</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>49.11</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>GLYPHOSATE AE 500/720</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>58601058</v>
+      </c>
+      <c r="D19" t="n">
+        <v>292488147</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>27.17</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>MANCOZEB 750</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>60084147</v>
+      </c>
+      <c r="D20" t="n">
+        <v>181393072</v>
+      </c>
+      <c r="E20" t="n">
+        <v>8</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Índia</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Índia</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>16.34</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>2,4-D AE 670</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>59631692</v>
+      </c>
+      <c r="D21" t="n">
+        <v>148379345</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>CLETHODIM 240</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>52296729</v>
+      </c>
+      <c r="D22" t="n">
+        <v>566957308</v>
+      </c>
+      <c r="E22" t="n">
         <v>17</v>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>38089324</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>glyphosate AE 720</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>57.07</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>MANCOZEB 750</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>57684844</v>
+      </c>
+      <c r="D23" t="n">
+        <v>201684301</v>
+      </c>
+      <c r="E23" t="n">
+        <v>11</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Índia</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Colômbia</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>17.99</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>GLYPHOSATE AE 500/720</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
         <v>57445965</v>
       </c>
-      <c r="F19" t="n">
+      <c r="D24" t="n">
         <v>183416402</v>
       </c>
-      <c r="G19" t="n">
+      <c r="E24" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>38249986</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>mancozeb 750</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>6889844</v>
-      </c>
-      <c r="F20" t="n">
-        <v>16422420</v>
-      </c>
-      <c r="G20" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>29309039</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>clethodim 240</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>5884522</v>
-      </c>
-      <c r="F21" t="n">
-        <v>104172563</v>
-      </c>
-      <c r="G21" t="n">
-        <v>14</v>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>17.1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>2,4-D AE 670</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>57413461</v>
+      </c>
+      <c r="D25" t="n">
+        <v>119592088</v>
+      </c>
+      <c r="E25" t="n">
+        <v>9</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>10.88</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A22:A25"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>